--- a/AAII_Financials/Yearly/TEAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TEAM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>TEAM</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6572300</v>
+      </c>
+      <c r="E8" s="3">
         <v>5215300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4358600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3534600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2802900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2089100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1614200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1210100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>881000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>626700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>457100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>319500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>215100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>148500</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>943600</v>
+      </c>
+      <c r="E9" s="3">
         <v>894900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>803500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>633800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>452900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>331900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>268800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>210300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>172700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>119200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>75800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>52900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>38000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>33000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5628700</v>
+      </c>
+      <c r="E10" s="3">
         <v>4320500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3555100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2900900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2350000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1757300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1345400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>999800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>708300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>507500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>381300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>266600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>177100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>115500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3124800</v>
+      </c>
+      <c r="E12" s="3">
         <v>2669300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2184100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1869900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1291900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>933000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>763200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>579100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>415800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>310200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>208300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>140900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>78600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>57300</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,36 +999,39 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>263300</v>
+      </c>
+      <c r="E14" s="3">
         <v>23000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>12000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-25800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>72700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-48100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1041,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1031,57 +1050,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E15" s="3">
         <v>92400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>78700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>60900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>51700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>56000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>33200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>58200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>100</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6276600</v>
+      </c>
+      <c r="E17" s="3">
         <v>5345700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4475700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3879900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2732800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1947700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1270500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>927000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>682500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>462900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>319100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>193600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>135400</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>295700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-130400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-117100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-345200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>70100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>141400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-60400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-55800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,142 +1245,149 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E20" s="3">
         <v>27300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>19000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>11300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>429200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>618500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>338500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>535500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>405800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-65300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-57300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-295500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-307400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-421100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-291200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-553600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>35500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>23500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E22" s="3">
         <v>30600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>41500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>92600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>49600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>40200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6800</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-98900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-85400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-311100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-470900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-514400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-346200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-605600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-58100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-52400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11400</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E24" s="3">
         <v>157800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>215100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>175600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>48600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>55300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-15000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-9300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-256700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-486800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-519500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-579000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-350700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-637600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-113400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-37400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10800</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-256700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-486800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-519500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-579000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-350600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-637600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-113400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10800</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-27300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-19000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-11300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-429200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-618500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-338500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-535500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1700</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-256700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-486800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-519500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-579000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-350700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-637600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-113400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-37400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10800</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-256700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-486800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-519500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-579000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-350700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-637600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-113400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-37400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10800</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,152 +2159,162 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1239500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2512900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2176900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2102600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1385300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>919200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1480000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1268400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1410300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>244400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>259700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>187100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>116800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>424300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>162000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>58300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>86600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>313000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>676100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>445000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>323100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>305500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>483400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>30300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>778300</v>
+        <v>1391400</v>
       </c>
       <c r="E43" s="3">
+        <v>797400</v>
+      </c>
+      <c r="F43" s="3">
         <v>628000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>477700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>308100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>183400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>128200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>88300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>64400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,8 +2342,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2265,132 +2360,141 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E45" s="3">
         <v>69800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>69500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>178000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>328100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>216800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2797100</v>
+      </c>
+      <c r="E46" s="3">
         <v>3891200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3076300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2736400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1897000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1627500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2643800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2042100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1822000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>612500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>778500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>238600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>171200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>213100</v>
+      </c>
+      <c r="E47" s="3">
         <v>221900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>223200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>253800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>189400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>125300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>103900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,105 +2513,114 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E48" s="3">
         <v>274200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>258800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>265600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>377900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>271500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>315300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>81500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>58800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2735000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1549300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1587800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>796300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>823700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>850300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>774800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>759900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>375500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>432700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E52" s="3">
         <v>15400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>113400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>197500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>133000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>88300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>54100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6103500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6042000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5212100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4106800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3326800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2945300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3894100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2977300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2421800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1283900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>991000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>397200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>262000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,85 +2915,89 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>262600</v>
+      </c>
+      <c r="E57" s="3">
         <v>222100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>177500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>159300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>81200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>40400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E58" s="3">
         <v>50200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>49000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>82400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>40600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>394600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>923900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>853600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2878,138 +3011,147 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2593300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2305400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1902100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1486600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1151100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1646300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1891800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1323100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>339800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>314400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>226900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>177600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>122100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3571100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3180900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2610100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2027600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1594100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2310000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3018800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2329700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>444900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>326900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>236500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>188200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>126500</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1184400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1189200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1200400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1199900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1273900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>214100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>229800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>819600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3025,57 +3167,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E62" s="3">
         <v>48200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>39900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>217300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>62900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5045100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4696300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4179300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3452100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2999500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2650400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3318800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2411800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1514500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>389800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>259300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>207100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>136700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6105400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4241900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3204500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2510000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1869000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1812700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1116400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-765600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-128000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>414100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>263600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>49900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1058400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1345700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1032900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>654700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>327400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>294900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>575300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>565500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>907300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>894000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>731700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>190100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>125300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-256700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-486800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-519500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-579000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-350700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-637600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-113400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-37400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10800</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E83" s="3">
         <v>36900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>29000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>54900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>22200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>61500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1353100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1460400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1448200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>868100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>821000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>790000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>574200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>466300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>311500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>199400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>129500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>75300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>54300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-44900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-70600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-35700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-34200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-806900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-342300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-963700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>36500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>259300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-318900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-604200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-51700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-224600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-489500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-46600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1800500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-782600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-408200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-148400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-399300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1603400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-42600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>906800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>432800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1264500</v>
+      </c>
+      <c r="E102" s="3">
         <v>335600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>74200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>716600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>449000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-548800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>211500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-141900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1165900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>72600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>70300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>26600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>43400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
